--- a/data/trans_dic/P20-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P20-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,35</t>
+          <t>1,98; 6,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,2</t>
+          <t>5,48; 12,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,66</t>
+          <t>3,16; 8,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,37</t>
+          <t>2,29; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,39</t>
+          <t>2,64; 8,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,43</t>
+          <t>9,2; 17,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 16,04</t>
+          <t>8,35; 15,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,93</t>
+          <t>4,64; 8,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,37</t>
+          <t>2,68; 6,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,66</t>
+          <t>8,29; 13,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,17</t>
+          <t>6,44; 10,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,02</t>
+          <t>3,83; 6,8</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,49</t>
+          <t>3,58; 7,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,67</t>
+          <t>6,0; 11,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,28</t>
+          <t>2,66; 6,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,29</t>
+          <t>4,98; 10,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 12,41</t>
+          <t>6,89; 12,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 14,38</t>
+          <t>8,46; 14,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,58</t>
+          <t>4,92; 9,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,2</t>
+          <t>2,9; 6,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,01</t>
+          <t>5,83; 9,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,04</t>
+          <t>8,21; 12,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,0</t>
+          <t>4,14; 7,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,43</t>
+          <t>4,58; 7,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,94</t>
+          <t>1,11; 5,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,09</t>
+          <t>4,65; 10,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,03</t>
+          <t>1,46; 5,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,96</t>
+          <t>5,94; 11,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,68</t>
+          <t>2,79; 7,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,17</t>
+          <t>7,48; 14,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 13,86</t>
+          <t>7,0; 13,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,5</t>
+          <t>6,82; 12,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,12</t>
+          <t>2,42; 5,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,58</t>
+          <t>7,1; 11,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,78</t>
+          <t>4,71; 8,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,37</t>
+          <t>7,17; 11,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,83</t>
+          <t>1,02; 4,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,82</t>
+          <t>3,23; 8,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,6</t>
+          <t>5,1; 10,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,27</t>
+          <t>4,56; 11,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,11</t>
+          <t>3,23; 8,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 13,29</t>
+          <t>7,22; 13,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,44</t>
+          <t>5,56; 11,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,04</t>
+          <t>3,85; 10,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,36</t>
+          <t>2,46; 5,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,8</t>
+          <t>5,79; 9,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,26</t>
+          <t>5,96; 10,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,08</t>
+          <t>4,76; 9,84</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 10,2</t>
+          <t>3,51; 10,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,6</t>
+          <t>3,45; 10,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,73</t>
+          <t>1,83; 7,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,42</t>
+          <t>1,07; 4,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 14,42</t>
+          <t>5,42; 13,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 14,37</t>
+          <t>6,17; 14,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,05</t>
+          <t>2,71; 9,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,04</t>
+          <t>2,48; 5,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,86</t>
+          <t>5,59; 10,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,87</t>
+          <t>5,8; 11,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,35</t>
+          <t>2,9; 7,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,62</t>
+          <t>2,2; 4,72</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,76</t>
+          <t>2,07; 6,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,95</t>
+          <t>3,06; 9,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,25</t>
+          <t>4,48; 10,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,38</t>
+          <t>6,47; 12,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,14</t>
+          <t>7,48; 14,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,69</t>
+          <t>5,96; 13,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 15,26</t>
+          <t>6,77; 14,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,59</t>
+          <t>5,91; 11,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,95</t>
+          <t>5,46; 9,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,08</t>
+          <t>5,55; 9,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,39</t>
+          <t>6,42; 11,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,92</t>
+          <t>6,8; 10,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,05</t>
+          <t>4,06; 8,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,57</t>
+          <t>3,24; 6,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,92</t>
+          <t>2,65; 6,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,53</t>
+          <t>4,05; 7,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,8</t>
+          <t>6,38; 10,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,05</t>
+          <t>6,48; 10,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,59</t>
+          <t>5,1; 9,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,45</t>
+          <t>2,72; 8,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,49</t>
+          <t>5,68; 8,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,04</t>
+          <t>5,24; 8,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,97</t>
+          <t>4,33; 7,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,36</t>
+          <t>3,67; 7,33</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,95</t>
+          <t>2,29; 4,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,51</t>
+          <t>3,33; 6,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,36</t>
+          <t>3,27; 6,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,86</t>
+          <t>1,08; 3,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,35</t>
+          <t>4,59; 8,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,41</t>
+          <t>5,67; 9,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,83</t>
+          <t>4,37; 7,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,56</t>
+          <t>2,78; 5,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,13</t>
+          <t>3,9; 6,16</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,47</t>
+          <t>4,91; 7,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,47</t>
+          <t>4,28; 6,59</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,09</t>
+          <t>1,92; 4,24</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,92</t>
+          <t>3,49; 4,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,02</t>
+          <t>5,24; 6,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,6</t>
+          <t>4,09; 5,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,34</t>
+          <t>4,25; 6,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,44</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,53</t>
+          <t>8,58; 10,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,65</t>
+          <t>6,84; 8,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,82</t>
+          <t>4,81; 6,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,34</t>
+          <t>5,23; 6,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,48</t>
+          <t>7,14; 8,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,89</t>
+          <t>5,72; 6,93</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,32</t>
+          <t>4,86; 6,3</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5371; 17348</t>
+          <t>5402; 17637</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16141; 35959</t>
+          <t>16151; 37204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8921; 25432</t>
+          <t>9275; 24593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6499; 19841</t>
+          <t>7134; 20808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6778; 21895</t>
+          <t>6875; 21672</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26264; 50079</t>
+          <t>26422; 50291</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23724; 46294</t>
+          <t>24106; 45951</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13045; 25851</t>
+          <t>13449; 25764</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14986; 34020</t>
+          <t>14306; 34068</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47668; 79499</t>
+          <t>48222; 81116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37690; 65070</t>
+          <t>37498; 63841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22687; 42193</t>
+          <t>23018; 40852</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16028; 36929</t>
+          <t>17659; 38106</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30917; 58779</t>
+          <t>30220; 55973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13807; 31583</t>
+          <t>13360; 31514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28080; 53352</t>
+          <t>25820; 52692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36109; 62523</t>
+          <t>34725; 60453</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45621; 75321</t>
+          <t>44327; 75542</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25012; 50136</t>
+          <t>25758; 50201</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14567; 31953</t>
+          <t>14957; 33271</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57144; 89853</t>
+          <t>58154; 90188</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82554; 123641</t>
+          <t>84342; 125147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40917; 71785</t>
+          <t>42505; 73082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46925; 76807</t>
+          <t>47293; 79249</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2618; 15765</t>
+          <t>3544; 16774</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16435; 35948</t>
+          <t>15053; 35384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4572; 16027</t>
+          <t>4666; 16553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19122; 37797</t>
+          <t>18781; 37206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10256; 25748</t>
+          <t>9362; 24675</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24725; 48306</t>
+          <t>25509; 49400</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23471; 46610</t>
+          <t>23529; 45695</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24775; 43653</t>
+          <t>23811; 43266</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14573; 33485</t>
+          <t>15851; 36714</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47176; 76997</t>
+          <t>47232; 78392</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32139; 57495</t>
+          <t>30856; 55847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48158; 75651</t>
+          <t>47699; 73700</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3485; 13698</t>
+          <t>3649; 14584</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12448; 29258</t>
+          <t>12076; 30552</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18127; 39228</t>
+          <t>18873; 40134</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14474; 38358</t>
+          <t>14266; 36127</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12612; 30113</t>
+          <t>11998; 29777</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26980; 51709</t>
+          <t>28085; 51973</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20938; 44310</t>
+          <t>21549; 44446</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18844; 52517</t>
+          <t>18332; 50870</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18871; 39100</t>
+          <t>17907; 37498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44302; 74754</t>
+          <t>44174; 74779</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45817; 77686</t>
+          <t>45130; 77762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38791; 79490</t>
+          <t>37512; 77599</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7045; 20734</t>
+          <t>7142; 20598</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7850; 22541</t>
+          <t>7326; 22315</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4471; 16320</t>
+          <t>3864; 15110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1916; 7893</t>
+          <t>1907; 8083</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11744; 29937</t>
+          <t>11253; 28771</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13584; 31553</t>
+          <t>13545; 31253</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5467; 19781</t>
+          <t>5919; 19725</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5255; 12609</t>
+          <t>5185; 12454</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22884; 44645</t>
+          <t>22992; 44680</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24621; 46965</t>
+          <t>25056; 48565</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12978; 31597</t>
+          <t>12482; 32113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8683; 17886</t>
+          <t>8529; 18296</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5623; 18299</t>
+          <t>5608; 17664</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8273; 24526</t>
+          <t>8394; 27264</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12072; 29603</t>
+          <t>11792; 28900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17816; 33389</t>
+          <t>17438; 33372</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21270; 42114</t>
+          <t>20812; 41407</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18638; 38327</t>
+          <t>16679; 37151</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18915; 41687</t>
+          <t>18485; 40195</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15841; 29789</t>
+          <t>15196; 29704</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30059; 54609</t>
+          <t>29999; 54059</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30253; 55845</t>
+          <t>30725; 55110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34374; 61052</t>
+          <t>34427; 63174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35719; 57539</t>
+          <t>35820; 57484</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25298; 49482</t>
+          <t>24981; 49589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20788; 43520</t>
+          <t>21444; 45858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16100; 38897</t>
+          <t>17402; 39699</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25427; 47037</t>
+          <t>25296; 47363</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41433; 68901</t>
+          <t>40702; 68452</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44247; 76653</t>
+          <t>44985; 74690</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36585; 66330</t>
+          <t>35242; 65287</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23469; 71728</t>
+          <t>23121; 72584</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71539; 106428</t>
+          <t>71182; 108854</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69801; 109045</t>
+          <t>71080; 109840</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58833; 93931</t>
+          <t>58346; 95353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53088; 108383</t>
+          <t>54117; 107958</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17195; 36794</t>
+          <t>17018; 37066</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26620; 50723</t>
+          <t>25922; 50633</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25353; 49509</t>
+          <t>25453; 49533</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9137; 35857</t>
+          <t>10070; 36740</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36801; 65431</t>
+          <t>35982; 64259</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47155; 77511</t>
+          <t>46737; 78440</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36857; 64692</t>
+          <t>36083; 65338</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20811; 39772</t>
+          <t>19854; 38869</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60554; 93643</t>
+          <t>59551; 94137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>79903; 119808</t>
+          <t>78746; 117635</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66656; 103906</t>
+          <t>68657; 105726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29810; 67320</t>
+          <t>31605; 69659</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>114463; 161027</t>
+          <t>114249; 160390</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>181142; 240563</t>
+          <t>179576; 238955</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138465; 190218</t>
+          <t>138742; 189650</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>148604; 219461</t>
+          <t>147065; 219115</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>221883; 285315</t>
+          <t>221283; 281499</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>304031; 374818</t>
+          <t>305250; 377915</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>241903; 306475</t>
+          <t>242355; 309016</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>177874; 249496</t>
+          <t>175872; 249986</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>350217; 422044</t>
+          <t>347926; 424115</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>501689; 591963</t>
+          <t>498597; 594004</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>396890; 477952</t>
+          <t>396945; 480834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>348675; 450091</t>
+          <t>346082; 448675</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P20-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,46</t>
+          <t>2,02; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,62</t>
+          <t>5,75; 12,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,37</t>
+          <t>3,02; 8,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,68</t>
+          <t>2,01; 6,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,31</t>
+          <t>2,3; 8,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 17,51</t>
+          <t>9,32; 17,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 15,92</t>
+          <t>8,11; 15,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,9</t>
+          <t>5,09; 9,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,38</t>
+          <t>2,85; 6,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,94</t>
+          <t>8,55; 13,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,96</t>
+          <t>6,3; 11,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,8</t>
+          <t>4,08; 7,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,73</t>
+          <t>3,37; 7,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,12</t>
+          <t>5,93; 11,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,27</t>
+          <t>2,65; 6,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,16</t>
+          <t>5,42; 10,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,0</t>
+          <t>7,05; 12,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,42</t>
+          <t>8,72; 14,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,6</t>
+          <t>4,78; 9,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,46</t>
+          <t>2,99; 6,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,05</t>
+          <t>5,77; 9,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 12,18</t>
+          <t>8,17; 12,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,13</t>
+          <t>4,14; 7,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,67</t>
+          <t>4,64; 7,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,26</t>
+          <t>0,91; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,92</t>
+          <t>4,9; 10,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,2</t>
+          <t>1,44; 5,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,77</t>
+          <t>6,07; 12,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,36</t>
+          <t>2,92; 7,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,49</t>
+          <t>7,59; 14,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 13,59</t>
+          <t>6,95; 13,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,39</t>
+          <t>6,65; 12,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,61</t>
+          <t>2,34; 5,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,79</t>
+          <t>7,16; 11,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,53</t>
+          <t>4,79; 8,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,08</t>
+          <t>7,14; 11,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,08</t>
+          <t>0,96; 3,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,17</t>
+          <t>3,37; 7,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,85</t>
+          <t>5,25; 10,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,56</t>
+          <t>4,95; 12,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,02</t>
+          <t>3,31; 7,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 13,36</t>
+          <t>7,18; 13,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,48</t>
+          <t>5,71; 11,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,69</t>
+          <t>6,31; 13,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,14</t>
+          <t>2,34; 5,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,8</t>
+          <t>5,98; 9,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,27</t>
+          <t>5,9; 10,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,84</t>
+          <t>6,15; 11,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,13</t>
+          <t>3,81; 10,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,5</t>
+          <t>3,71; 10,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,15</t>
+          <t>2,21; 7,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,52</t>
+          <t>1,05; 4,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 13,85</t>
+          <t>5,37; 13,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 14,23</t>
+          <t>6,08; 14,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,02</t>
+          <t>2,5; 9,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,97</t>
+          <t>2,52; 5,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,87</t>
+          <t>5,3; 10,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 11,24</t>
+          <t>5,84; 11,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,47</t>
+          <t>2,88; 6,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,72</t>
+          <t>2,1; 4,47</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,52</t>
+          <t>2,1; 6,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,95</t>
+          <t>3,09; 9,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,98</t>
+          <t>4,57; 11,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,47; 12,38</t>
+          <t>6,62; 12,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,89</t>
+          <t>7,65; 15,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,27</t>
+          <t>6,44; 13,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 14,72</t>
+          <t>7,05; 14,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 11,56</t>
+          <t>6,03; 11,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,85</t>
+          <t>5,63; 9,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,95</t>
+          <t>5,58; 10,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,78</t>
+          <t>6,83; 11,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,91</t>
+          <t>6,69; 10,81</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,06</t>
+          <t>4,22; 7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,92</t>
+          <t>3,07; 6,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,05</t>
+          <t>2,58; 5,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,59</t>
+          <t>4,27; 7,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,73</t>
+          <t>6,45; 10,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,76</t>
+          <t>6,57; 10,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,44</t>
+          <t>5,18; 9,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,55</t>
+          <t>6,43; 10,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,69</t>
+          <t>5,75; 8,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,1</t>
+          <t>5,2; 8,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,07</t>
+          <t>4,39; 7,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,33</t>
+          <t>6,04; 8,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,98</t>
+          <t>2,39; 5,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,5</t>
+          <t>3,4; 6,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,36</t>
+          <t>3,22; 6,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,96</t>
+          <t>2,24; 4,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,2</t>
+          <t>4,84; 8,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,52</t>
+          <t>5,65; 9,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,91</t>
+          <t>4,39; 7,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,43</t>
+          <t>2,75; 5,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,16</t>
+          <t>3,91; 6,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,34</t>
+          <t>4,97; 7,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,59</t>
+          <t>4,23; 6,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,24</t>
+          <t>2,74; 4,52</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,9</t>
+          <t>3,48; 4,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,98</t>
+          <t>5,34; 7,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,59</t>
+          <t>4,15; 5,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,33</t>
+          <t>5,07; 6,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,33</t>
+          <t>6,44; 8,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,62</t>
+          <t>8,56; 10,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,72</t>
+          <t>6,86; 8,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,83</t>
+          <t>5,86; 7,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,37</t>
+          <t>5,19; 6,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,51</t>
+          <t>7,18; 8,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,93</t>
+          <t>5,7; 6,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,3</t>
+          <t>5,66; 6,71</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>33882</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5402; 17637</t>
+          <t>5505; 17838</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16151; 37204</t>
+          <t>16941; 37212</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9275; 24593</t>
+          <t>8883; 23612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7134; 20808</t>
+          <t>6394; 19267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6875; 21672</t>
+          <t>6009; 21637</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26422; 50291</t>
+          <t>26772; 50689</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24106; 45951</t>
+          <t>23418; 45349</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13449; 25764</t>
+          <t>16086; 30616</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14306; 34068</t>
+          <t>15214; 34770</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48222; 81116</t>
+          <t>49748; 80256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37498; 63841</t>
+          <t>36684; 64662</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23018; 40852</t>
+          <t>25876; 45025</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>65335</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17659; 38106</t>
+          <t>16599; 38134</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30220; 55973</t>
+          <t>29836; 57602</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13360; 31514</t>
+          <t>13319; 32165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25820; 52692</t>
+          <t>28770; 56863</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34725; 60453</t>
+          <t>35539; 61405</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44327; 75542</t>
+          <t>45690; 74151</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25758; 50201</t>
+          <t>25010; 47910</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14957; 33271</t>
+          <t>16359; 35004</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58154; 90188</t>
+          <t>57571; 91396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84342; 125147</t>
+          <t>83970; 124612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42505; 73082</t>
+          <t>42494; 72878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47293; 79249</t>
+          <t>50023; 83107</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>59857</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3544; 16774</t>
+          <t>2891; 15058</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15053; 35384</t>
+          <t>15884; 35185</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4666; 16553</t>
+          <t>4594; 16641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18781; 37206</t>
+          <t>19195; 38386</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9362; 24675</t>
+          <t>9806; 25321</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25509; 49400</t>
+          <t>25893; 48501</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23529; 45695</t>
+          <t>23377; 44706</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23811; 43266</t>
+          <t>23705; 43599</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15851; 36714</t>
+          <t>15279; 35790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47232; 78392</t>
+          <t>47642; 77943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30856; 55847</t>
+          <t>31376; 56275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47699; 73700</t>
+          <t>47983; 74263</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>65865</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3649; 14584</t>
+          <t>3447; 13894</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12076; 30552</t>
+          <t>12616; 29661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18873; 40134</t>
+          <t>19423; 39747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14266; 36127</t>
+          <t>18463; 45676</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11998; 29777</t>
+          <t>12290; 29390</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28085; 51973</t>
+          <t>27911; 51778</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21549; 44446</t>
+          <t>22096; 44648</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18332; 50870</t>
+          <t>26644; 57004</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17907; 37498</t>
+          <t>17089; 37503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44174; 74779</t>
+          <t>45639; 75169</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45130; 77762</t>
+          <t>44709; 77265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37512; 77599</t>
+          <t>48915; 90493</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13513</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7142; 20598</t>
+          <t>7752; 21780</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7326; 22315</t>
+          <t>7895; 21874</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3864; 15110</t>
+          <t>4675; 15041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1907; 8083</t>
+          <t>2154; 8668</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11253; 28771</t>
+          <t>11150; 28515</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13545; 31253</t>
+          <t>13343; 31688</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5919; 19725</t>
+          <t>5465; 20327</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5185; 12454</t>
+          <t>5726; 13270</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22992; 44680</t>
+          <t>21784; 42929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25056; 48565</t>
+          <t>25228; 49319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12482; 32113</t>
+          <t>12384; 29895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8529; 18296</t>
+          <t>9110; 19371</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>46563</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5608; 17664</t>
+          <t>5686; 17925</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8394; 27264</t>
+          <t>8455; 25521</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11792; 28900</t>
+          <t>12018; 29223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17438; 33372</t>
+          <t>17920; 32736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20812; 41407</t>
+          <t>21288; 42320</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16679; 37151</t>
+          <t>18037; 38572</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18485; 40195</t>
+          <t>19247; 40518</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15196; 29704</t>
+          <t>15917; 29684</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29999; 54059</t>
+          <t>30920; 54276</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30725; 55110</t>
+          <t>30937; 56301</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34427; 63174</t>
+          <t>36599; 61742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35820; 57484</t>
+          <t>35761; 57777</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>107235</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24981; 49589</t>
+          <t>25963; 48451</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21444; 45858</t>
+          <t>20357; 44106</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17402; 39699</t>
+          <t>16955; 38936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25296; 47363</t>
+          <t>30726; 56984</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40702; 68452</t>
+          <t>41133; 68911</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44985; 74690</t>
+          <t>45596; 75307</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35242; 65287</t>
+          <t>35836; 65700</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23121; 72584</t>
+          <t>49638; 77503</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71182; 108854</t>
+          <t>72120; 108763</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71080; 109840</t>
+          <t>70484; 112850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58346; 95353</t>
+          <t>59138; 95139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>54117; 107958</t>
+          <t>90130; 128326</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>58395</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17018; 37066</t>
+          <t>17803; 37486</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25922; 50633</t>
+          <t>26515; 50732</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25453; 49533</t>
+          <t>25062; 49545</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10070; 36740</t>
+          <t>17852; 37842</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35982; 64259</t>
+          <t>37952; 66380</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46737; 78440</t>
+          <t>46566; 77416</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36083; 65338</t>
+          <t>36261; 64275</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>19854; 38869</t>
+          <t>22802; 44335</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>59551; 94137</t>
+          <t>59726; 94225</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>78746; 117635</t>
+          <t>79743; 120072</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>68657; 105726</t>
+          <t>67899; 105249</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>31605; 69659</t>
+          <t>44596; 73680</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>114249; 160390</t>
+          <t>113852; 161439</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>179576; 238955</t>
+          <t>182917; 241405</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138742; 189650</t>
+          <t>140882; 189532</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147065; 219115</t>
+          <t>179132; 233033</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>221283; 281499</t>
+          <t>217521; 281291</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>305250; 377915</t>
+          <t>304653; 372775</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>242355; 309016</t>
+          <t>243318; 308758</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>175872; 249986</t>
+          <t>218887; 275599</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>347926; 424115</t>
+          <t>345434; 423699</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>498597; 594004</t>
+          <t>501056; 597539</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>396945; 480834</t>
+          <t>395829; 484261</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>346082; 448675</t>
+          <t>411442; 487883</t>
         </is>
       </c>
     </row>
